--- a/artfynd/A 16179-2025 artfynd.xlsx
+++ b/artfynd/A 16179-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>85540090</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
+        <v>100682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423677.9230044554</v>
+        <v>423678</v>
       </c>
       <c r="R3" t="n">
-        <v>6477361.395684731</v>
+        <v>6477361</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +869,9 @@
           <t>2020-05-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-05-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 16179-2025 artfynd.xlsx
+++ b/artfynd/A 16179-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>85540084</v>
       </c>
       <c r="B2" t="n">
-        <v>101859</v>
+        <v>103685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>423653.7185258053</v>
+        <v>423654</v>
       </c>
       <c r="R2" t="n">
-        <v>6477277.014411097</v>
+        <v>6477277</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +748,9 @@
           <t>2020-05-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-05-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,7 +789,7 @@
         <v>85540090</v>
       </c>
       <c r="B3" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +900,7 @@
         <v>85540083</v>
       </c>
       <c r="B4" t="n">
-        <v>104654</v>
+        <v>106543</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423653.7185258053</v>
+        <v>423654</v>
       </c>
       <c r="R4" t="n">
-        <v>6477277.014411097</v>
+        <v>6477277</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +970,9 @@
           <t>2020-05-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-05-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 16179-2025 artfynd.xlsx
+++ b/artfynd/A 16179-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -900,7 +900,7 @@
         <v>85540083</v>
       </c>
       <c r="B4" t="n">
-        <v>106543</v>
+        <v>106544</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 16179-2025 artfynd.xlsx
+++ b/artfynd/A 16179-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 16179-2025 artfynd.xlsx
+++ b/artfynd/A 16179-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 16179-2025 artfynd.xlsx
+++ b/artfynd/A 16179-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 16179-2025 artfynd.xlsx
+++ b/artfynd/A 16179-2025 artfynd.xlsx
@@ -1011,12 +1011,7 @@
         <v>85813720</v>
       </c>
       <c r="B5" t="n">
-        <v>57000</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423572.9178033528</v>
+        <v>423573</v>
       </c>
       <c r="R5" t="n">
-        <v>6477331.488032976</v>
+        <v>6477331</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 16179-2025 artfynd.xlsx
+++ b/artfynd/A 16179-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>85813720</v>
       </c>
       <c r="B5" t="n">
-        <v>58581</v>
+        <v>58582</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16179-2025 artfynd.xlsx
+++ b/artfynd/A 16179-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>85813720</v>
       </c>
       <c r="B5" t="n">
-        <v>58582</v>
+        <v>58586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16179-2025 artfynd.xlsx
+++ b/artfynd/A 16179-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>85813720</v>
       </c>
       <c r="B5" t="n">
-        <v>58586</v>
+        <v>58587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16179-2025 artfynd.xlsx
+++ b/artfynd/A 16179-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,65 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85540084</v>
+        <v>87063098</v>
       </c>
       <c r="B2" t="n">
-        <v>103707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220464</v>
+        <v>101002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lundbräsma</t>
+          <t>Ädelguldbagge</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cardamine impatiens</t>
+          <t>Gnorimus nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jättadalen, Vg</t>
+          <t>Paradiset, Öglunda, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>423654</v>
+        <v>423679</v>
       </c>
       <c r="R2" t="n">
-        <v>6477277</v>
+        <v>6477388</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +757,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2020-07-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2020-07-23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Satt i blomställning av älgört.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,72 +776,84 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85540090</v>
+        <v>85813720</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103051</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenfink</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carpodacus erythrinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Pallas, 1770)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jättadalen, Vg</t>
+          <t>Engelbrektsgården, Billingen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423678</v>
+        <v>423573</v>
       </c>
       <c r="R3" t="n">
-        <v>6477361</v>
+        <v>6477331</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -856,17 +880,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2020-05-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+          <t>2020-05-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,31 +910,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Staffan Pehrson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+          <t>Staffan Pehrson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>85540083</v>
       </c>
       <c r="B4" t="n">
-        <v>106566</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107719</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,65 +1028,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>85813720</v>
+        <v>85540084</v>
       </c>
       <c r="B5" t="n">
-        <v>58591</v>
+        <v>104808</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103051</v>
+        <v>220464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenfink</t>
+          <t>Lundbräsma</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carpodacus erythrinus</t>
+          <t>Cardamine impatiens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Engelbrektsgården, Billingen, Vg</t>
+          <t>Jättadalen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423573</v>
+        <v>423654</v>
       </c>
       <c r="R5" t="n">
-        <v>6477331</v>
+        <v>6477277</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,22 +1093,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-05-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-05-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2020-05-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1118,125 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Staffan Pehrson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Staffan Pehrson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>85540090</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Jättadalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>423678</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6477361</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skara</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Öglunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-05-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-05-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16179-2025 artfynd.xlsx
+++ b/artfynd/A 16179-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87063098</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85813720</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85540083</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85540084</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,8 +1262,20 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85540090</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>